--- a/PTP-Project-Setup-Template.xlsx
+++ b/PTP-Project-Setup-Template.xlsx
@@ -2374,7 +2374,7 @@
   <sheetPr>
     <tabColor rgb="5892A0"/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -3121,7 +3121,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:C1"/>
@@ -3137,7 +3136,7 @@
     <mergeCell ref="A12:C12"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Permission Level" error="Please select a permission level from the dropdown list." sqref="C16:C74">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Permission Level" error="Please select a permission level from the dropdown list." sqref="C15:C73">
       <formula1>PermissionLevels</formula1>
     </dataValidation>
   </dataValidations>

--- a/PTP-Project-Setup-Template.xlsx
+++ b/PTP-Project-Setup-Template.xlsx
@@ -135,10 +135,10 @@
     <t>Use the dropdown menus where available — they ensure the data is in the correct format.</t>
   </si>
   <si>
-    <t>The Reference tab contains the dropdown lists for permission levels and issue types.</t>
-  </si>
-  <si>
-    <t>The Roles tab contains the dropdown source for Permissions and the trade list on Companies.</t>
+    <t>The Reference tab contains the dropdown lists for permission levels, issue statuses, issue types, assignee types, and root cause categories.</t>
+  </si>
+  <si>
+    <t>The Roles tab is the source of the Role Name dropdown on the Permissions tab.</t>
   </si>
   <si>
     <t>Important Notes</t>
@@ -1757,7 +1757,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" ht="40" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
